--- a/My project/Assets/StreamingAssets/Stage00.xlsx
+++ b/My project/Assets/StreamingAssets/Stage00.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\新しいフォルダー\My project\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\team5\My project\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{177035E0-C023-4654-8F4B-1CEDA356BF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B639B9-FD2E-4225-AA62-94D36D404492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{7A560D67-D24D-4CE2-A9EC-D6C33276A18D}"/>
   </bookViews>
@@ -692,10 +692,7 @@
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="L6">
+      <c r="F6">
         <v>5</v>
       </c>
       <c r="Q6">

--- a/My project/Assets/StreamingAssets/Stage00.xlsx
+++ b/My project/Assets/StreamingAssets/Stage00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\team5\My project\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B639B9-FD2E-4225-AA62-94D36D404492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA1CC3F-74D7-47B6-BF95-5DB57B73273C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{7A560D67-D24D-4CE2-A9EC-D6C33276A18D}"/>
   </bookViews>
@@ -689,7 +689,7 @@
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="E6">
+      <c r="D6">
         <v>2</v>
       </c>
       <c r="F6">
